--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_OV_Fiets.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>412.936847725596</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>293.7040883048616</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>247.5866598743754</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>229.1525758334074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2108.712530461779</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1492.364264413481</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1288.178366683002</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1159.863934197643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>196.6119278183984</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>136.2395603756288</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>119.6487339999811</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>109.4132806796198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>35.10725127135111</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>22.9913519096603</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>19.94071111510026</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>19.71785220273537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>109.6583159454891</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>75.12354742175509</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>66.16126303641012</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>61.19905936475248</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
